--- a/cosmetics-catalog.xlsx
+++ b/cosmetics-catalog.xlsx
@@ -2084,6 +2084,11 @@
           <t xml:space="preserve">Vichy</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosmetics/vichy-liftactiv-vit-c-skin-cor-20ml-sp-por-3337875796583.jpg</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">MB453802</t>
@@ -3306,6 +3311,11 @@
           <t xml:space="preserve">Vichy</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosmetics/vichy-f-dermablend-coverflow-inter-15-t30m-3337871332297.png</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">M9005604</t>
@@ -11508,6 +11518,11 @@
           <t xml:space="preserve">La Roche-Posay</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosmetics/la-roche-posay-hyalu-b5-suractivated-serum-50ml-3337875920568.png</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t xml:space="preserve">VGR08457</t>
@@ -12081,6 +12096,11 @@
           <t xml:space="preserve">La Roche-Posay</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosmetics/la-roche-posay-retinol-lrp-red-retinol-yeux-15ml-3337872414039.jpg</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t xml:space="preserve">VGR07424</t>
@@ -12483,6 +12503,11 @@
       <c r="E241" t="inlineStr">
         <is>
           <t xml:space="preserve">La Roche-Posay</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosmetics/la-roche-posay-mela-b3-cleanser-200ml-3337875890069.jpg</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
